--- a/test/Блок спецификации.xlsx
+++ b/test/Блок спецификации.xlsx
@@ -1,124 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vorob\Documents\NORDFOX\Проект программы раскроя профилей\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C499D14-B8D3-4BA6-B8EA-4C57C82E81B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{018F94E7-B57A-4709-8393-56CD6B05CC85}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-48780" yWindow="-1785" windowWidth="21600" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Модуль М1</t>
-  </si>
-  <si>
-    <t>Тип профиля</t>
-  </si>
-  <si>
-    <t>Длина</t>
-  </si>
-  <si>
-    <t>Угол запила</t>
-  </si>
-  <si>
-    <t>Количество</t>
-  </si>
-  <si>
-    <t>QR-код</t>
-  </si>
-  <si>
-    <t>Наименование</t>
-  </si>
-  <si>
-    <t>№ п/п</t>
-  </si>
-  <si>
-    <t>СК-0-1045П</t>
-  </si>
-  <si>
-    <t>СК-0-1045Л</t>
-  </si>
-  <si>
-    <t>Р-1-3030В</t>
-  </si>
-  <si>
-    <t>Р-1-3030Н</t>
-  </si>
-  <si>
-    <t>СС-1-456</t>
-  </si>
-  <si>
-    <t>СК- стойка крайняя</t>
-  </si>
-  <si>
-    <t>СС - стойка средняя</t>
-  </si>
-  <si>
-    <t>Р - ригель</t>
-  </si>
-  <si>
-    <t>Л - левая</t>
-  </si>
-  <si>
-    <t>П- правая</t>
-  </si>
-  <si>
-    <t>В - верхний</t>
-  </si>
-  <si>
-    <t>Н - нижний</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -141,31 +57,133 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -465,164 +483,559 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F74B5156-690A-4084-875F-496A46CFD8AC}">
-  <dimension ref="F8:L18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col width="16.7109375" customWidth="1" min="7" max="7"/>
+    <col width="12.7109375" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="6.85546875" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="11.85546875" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="18.7109375" customWidth="1" min="11" max="11"/>
+    <col width="11.5703125" bestFit="1" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="8" spans="6:12" x14ac:dyDescent="0.25">
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="6:12" x14ac:dyDescent="0.25">
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="6:12" x14ac:dyDescent="0.25">
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="6:12" x14ac:dyDescent="0.25">
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="6:12" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="6:12" x14ac:dyDescent="0.25">
-      <c r="F13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="6:12" x14ac:dyDescent="0.25">
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="1">
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>№ п/п</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>Тип профиля</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>Длина</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>Угол запила</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>Сторона запила</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
+          <t>QR-код</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="F14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Модуль М1</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>СК-0-1045</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n">
         <v>1045</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>Левая</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1" t="n"/>
+    </row>
+    <row r="15">
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t>Правая</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="1" t="n"/>
+    </row>
+    <row r="16">
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>СК-1-1045</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>1045</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="K14" s="1">
-        <v>1</v>
-      </c>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="6:12" x14ac:dyDescent="0.25">
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="1">
-        <v>1045</v>
-      </c>
-      <c r="J15" s="1">
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>Левая</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1" t="n"/>
+    </row>
+    <row r="17">
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>Правая</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="1" t="n"/>
+    </row>
+    <row r="18">
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Р-1-3030</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3030</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>Левая</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1" t="n"/>
+    </row>
+    <row r="19">
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>Правая</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="1" t="n"/>
+    </row>
+    <row r="20">
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Р-2-3030</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>3030</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="K15" s="1">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="6:12" x14ac:dyDescent="0.25">
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="1">
-        <v>3030</v>
-      </c>
-      <c r="J16" s="1">
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>Левая</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1" t="n"/>
+    </row>
+    <row r="21">
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>Правая</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="1" t="n"/>
+    </row>
+    <row r="22">
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>СС-1-456</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>456</v>
+      </c>
+      <c r="J22" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="K16" s="1">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="6:12" x14ac:dyDescent="0.25">
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="1">
-        <v>3030</v>
-      </c>
-      <c r="J17" s="1">
+      <c r="K22" s="1" t="inlineStr">
+        <is>
+          <t>Левая</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1" t="n"/>
+    </row>
+    <row r="23">
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="K23" s="1" t="inlineStr">
+        <is>
+          <t>Правая</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="1" t="n"/>
+    </row>
+    <row r="24">
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>СС-1-457</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>457</v>
+      </c>
+      <c r="J24" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="K17" s="1">
-        <v>1</v>
-      </c>
-      <c r="L17" s="1"/>
-    </row>
-    <row r="18" spans="6:12" x14ac:dyDescent="0.25">
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I18" s="3">
-        <v>456</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K24" s="1" t="inlineStr">
+        <is>
+          <t>Левая</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1" t="n"/>
+    </row>
+    <row r="25">
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="K25" s="1" t="inlineStr">
+        <is>
+          <t>Правая</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="1" t="n"/>
+    </row>
+    <row r="26">
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>СС-2-458</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>458</v>
+      </c>
+      <c r="J26" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="K18" s="3">
-        <v>1</v>
-      </c>
-      <c r="L18" s="1"/>
+      <c r="K26" s="1" t="inlineStr">
+        <is>
+          <t>Левая</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="1" t="n"/>
+    </row>
+    <row r="27">
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="K27" s="1" t="inlineStr">
+        <is>
+          <t>Правая</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="1" t="n"/>
+    </row>
+    <row r="28">
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>СС-3-459</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>459</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>Левая</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1" t="n"/>
+    </row>
+    <row r="29">
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K29" s="1" t="inlineStr">
+        <is>
+          <t>Правая</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="1" t="n"/>
+    </row>
+    <row r="30">
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>СС-0-451</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>451</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="K30" s="1" t="inlineStr">
+        <is>
+          <t>Левая</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1" t="n"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="K31" s="1" t="inlineStr">
+        <is>
+          <t>Правая</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="1" t="n"/>
+    </row>
+    <row r="32">
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>L15</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="K32" s="1" t="inlineStr">
+        <is>
+          <t>Левая</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1" t="n"/>
+    </row>
+    <row r="33">
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="K33" s="1" t="inlineStr">
+        <is>
+          <t>Правая</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="1" t="n"/>
+    </row>
+    <row r="34">
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>DT21</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="K34" s="1" t="inlineStr">
+        <is>
+          <t>Левая</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="1" t="n"/>
+    </row>
+    <row r="35">
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+      <c r="J35" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="K35" s="1" t="inlineStr">
+        <is>
+          <t>Правая</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="G14:G18"/>
-    <mergeCell ref="F14:F18"/>
+  <mergeCells count="35">
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="L32:L33"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="G14:G35"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="L34:L35"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="F14:F35"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="L16:L17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
